--- a/docs/test-data/test-full-coverage-import-suite/default-tenant-config-package-test.xlsx
+++ b/docs/test-data/test-full-coverage-import-suite/default-tenant-config-package-test.xlsx
@@ -1,20 +1,20 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="job_definition" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="file_channel_config" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="alert_routing_config" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="pipeline_definition" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="pipeline_step_definition" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="workflow_definition" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet name="workflow_node" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet name="workflow_edge" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="job_definition" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="file_channel_config" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="file_template_config" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="pipeline_definition" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="pipeline_step_definition" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="workflow_definition" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="workflow_node" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="workflow_edge" sheetId="8" state="visible" r:id="rId8"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1036,8 +1036,51 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M1"/>
+  <dimension ref="A1:AO4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="13" customWidth="1" min="1" max="1"/>
+    <col width="17" customWidth="1" min="2" max="2"/>
+    <col width="28" customWidth="1" min="3" max="3"/>
+    <col width="17" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="20" customWidth="1" min="6" max="6"/>
+    <col width="12" customWidth="1" min="7" max="7"/>
+    <col width="18" customWidth="1" min="8" max="8"/>
+    <col width="12" customWidth="1" min="9" max="9"/>
+    <col width="18" customWidth="1" min="10" max="10"/>
+    <col width="13" customWidth="1" min="11" max="11"/>
+    <col width="14" customWidth="1" min="12" max="12"/>
+    <col width="15" customWidth="1" min="13" max="13"/>
+    <col width="17" customWidth="1" min="14" max="14"/>
+    <col width="15" customWidth="1" min="15" max="15"/>
+    <col width="15" customWidth="1" min="16" max="16"/>
+    <col width="19" customWidth="1" min="17" max="17"/>
+    <col width="20" customWidth="1" min="18" max="18"/>
+    <col width="17" customWidth="1" min="19" max="19"/>
+    <col width="17" customWidth="1" min="20" max="20"/>
+    <col width="16" customWidth="1" min="21" max="21"/>
+    <col width="28" customWidth="1" min="22" max="22"/>
+    <col width="34" customWidth="1" min="23" max="23"/>
+    <col width="34" customWidth="1" min="24" max="24"/>
+    <col width="22" customWidth="1" min="25" max="25"/>
+    <col width="34" customWidth="1" min="26" max="26"/>
+    <col width="34" customWidth="1" min="27" max="27"/>
+    <col width="21" customWidth="1" min="28" max="28"/>
+    <col width="13" customWidth="1" min="29" max="29"/>
+    <col width="14" customWidth="1" min="30" max="30"/>
+    <col width="14" customWidth="1" min="31" max="31"/>
+    <col width="27" customWidth="1" min="32" max="32"/>
+    <col width="30" customWidth="1" min="33" max="33"/>
+    <col width="23" customWidth="1" min="34" max="34"/>
+    <col width="30" customWidth="1" min="35" max="35"/>
+    <col width="22" customWidth="1" min="36" max="36"/>
+    <col width="30" customWidth="1" min="37" max="37"/>
+    <col width="20" customWidth="1" min="38" max="38"/>
+    <col width="12" customWidth="1" min="39" max="39"/>
+    <col width="12" customWidth="1" min="40" max="40"/>
+    <col width="34" customWidth="1" min="41" max="41"/>
+  </cols>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
@@ -1047,62 +1090,721 @@
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>route_code</t>
+          <t>template_code</t>
         </is>
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>route_name</t>
+          <t>template_name</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>team</t>
+          <t>template_type</t>
         </is>
       </c>
       <c r="E1" t="inlineStr">
         <is>
-          <t>alert_group</t>
+          <t>biz_type</t>
         </is>
       </c>
       <c r="F1" t="inlineStr">
         <is>
-          <t>severity</t>
+          <t>file_format_type</t>
         </is>
       </c>
       <c r="G1" t="inlineStr">
         <is>
-          <t>receiver</t>
+          <t>charset</t>
         </is>
       </c>
       <c r="H1" t="inlineStr">
         <is>
-          <t>group_by</t>
+          <t>target_charset</t>
         </is>
       </c>
       <c r="I1" t="inlineStr">
         <is>
-          <t>group_wait_seconds</t>
+          <t>with_bom</t>
         </is>
       </c>
       <c r="J1" t="inlineStr">
         <is>
-          <t>group_interval_seconds</t>
+          <t>line_separator</t>
         </is>
       </c>
       <c r="K1" t="inlineStr">
         <is>
-          <t>repeat_interval_seconds</t>
+          <t>delimiter</t>
         </is>
       </c>
       <c r="L1" t="inlineStr">
         <is>
+          <t>quote_char</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>escape_char</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>record_length</t>
+        </is>
+      </c>
+      <c r="O1" t="inlineStr">
+        <is>
+          <t>header_rows</t>
+        </is>
+      </c>
+      <c r="P1" t="inlineStr">
+        <is>
+          <t>footer_rows</t>
+        </is>
+      </c>
+      <c r="Q1" t="inlineStr">
+        <is>
+          <t>header_template</t>
+        </is>
+      </c>
+      <c r="R1" t="inlineStr">
+        <is>
+          <t>trailer_template</t>
+        </is>
+      </c>
+      <c r="S1" t="inlineStr">
+        <is>
+          <t>checksum_type</t>
+        </is>
+      </c>
+      <c r="T1" t="inlineStr">
+        <is>
+          <t>compress_type</t>
+        </is>
+      </c>
+      <c r="U1" t="inlineStr">
+        <is>
+          <t>encrypt_type</t>
+        </is>
+      </c>
+      <c r="V1" t="inlineStr">
+        <is>
+          <t>naming_rule</t>
+        </is>
+      </c>
+      <c r="W1" t="inlineStr">
+        <is>
+          <t>field_mappings</t>
+        </is>
+      </c>
+      <c r="X1" t="inlineStr">
+        <is>
+          <t>validation_rule_set</t>
+        </is>
+      </c>
+      <c r="Y1" t="inlineStr">
+        <is>
+          <t>default_query_code</t>
+        </is>
+      </c>
+      <c r="Z1" t="inlineStr">
+        <is>
+          <t>default_query_sql</t>
+        </is>
+      </c>
+      <c r="AA1" t="inlineStr">
+        <is>
+          <t>query_param_schema</t>
+        </is>
+      </c>
+      <c r="AB1" t="inlineStr">
+        <is>
+          <t>streaming_enabled</t>
+        </is>
+      </c>
+      <c r="AC1" t="inlineStr">
+        <is>
+          <t>page_size</t>
+        </is>
+      </c>
+      <c r="AD1" t="inlineStr">
+        <is>
+          <t>fetch_size</t>
+        </is>
+      </c>
+      <c r="AE1" t="inlineStr">
+        <is>
+          <t>chunk_size</t>
+        </is>
+      </c>
+      <c r="AF1" t="inlineStr">
+        <is>
+          <t>preview_masking_enabled</t>
+        </is>
+      </c>
+      <c r="AG1" t="inlineStr">
+        <is>
+          <t>error_line_masking_enabled</t>
+        </is>
+      </c>
+      <c r="AH1" t="inlineStr">
+        <is>
+          <t>log_masking_enabled</t>
+        </is>
+      </c>
+      <c r="AI1" t="inlineStr">
+        <is>
+          <t>content_encryption_enabled</t>
+        </is>
+      </c>
+      <c r="AJ1" t="inlineStr">
+        <is>
+          <t>encryption_key_ref</t>
+        </is>
+      </c>
+      <c r="AK1" t="inlineStr">
+        <is>
+          <t>download_requires_approval</t>
+        </is>
+      </c>
+      <c r="AL1" t="inlineStr">
+        <is>
+          <t>masking_rule_set</t>
+        </is>
+      </c>
+      <c r="AM1" t="inlineStr">
+        <is>
           <t>enabled</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
+      <c r="AN1" t="inlineStr">
+        <is>
+          <t>version</t>
+        </is>
+      </c>
+      <c r="AO1" t="inlineStr">
         <is>
           <t>description</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>default-tenant</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>wf_probe_pipeline_TPL</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Probe PIPELINE文件模板</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>SHARED</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>WORKFLOW</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>DELIMITED</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>UTF-8</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>UTF-8</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>FALSE</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>\n</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>,</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>"</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>\</t>
+        </is>
+      </c>
+      <c r="N2" t="n">
+        <v>0</v>
+      </c>
+      <c r="O2" t="n">
+        <v>0</v>
+      </c>
+      <c r="P2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q2" t="inlineStr">
+        <is>
+          <t>{}</t>
+        </is>
+      </c>
+      <c r="R2" t="inlineStr">
+        <is>
+          <t>{}</t>
+        </is>
+      </c>
+      <c r="S2" t="inlineStr">
+        <is>
+          <t>NONE</t>
+        </is>
+      </c>
+      <c r="T2" t="inlineStr">
+        <is>
+          <t>NONE</t>
+        </is>
+      </c>
+      <c r="U2" t="inlineStr">
+        <is>
+          <t>NONE</t>
+        </is>
+      </c>
+      <c r="V2" t="inlineStr">
+        <is>
+          <t>wf_probe_pipeline_${batchDate}.csv</t>
+        </is>
+      </c>
+      <c r="W2" t="inlineStr">
+        <is>
+          <t>[{"source":"id","target":"ID"}]</t>
+        </is>
+      </c>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>{}</t>
+        </is>
+      </c>
+      <c r="AA2" t="inlineStr">
+        <is>
+          <t>{}</t>
+        </is>
+      </c>
+      <c r="AB2" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AC2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AD2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AE2" t="n">
+        <v>500</v>
+      </c>
+      <c r="AF2" t="inlineStr">
+        <is>
+          <t>FALSE</t>
+        </is>
+      </c>
+      <c r="AG2" t="inlineStr">
+        <is>
+          <t>FALSE</t>
+        </is>
+      </c>
+      <c r="AH2" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AI2" t="inlineStr">
+        <is>
+          <t>FALSE</t>
+        </is>
+      </c>
+      <c r="AK2" t="inlineStr">
+        <is>
+          <t>FALSE</t>
+        </is>
+      </c>
+      <c r="AM2" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AN2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO2" t="inlineStr">
+        <is>
+          <t>wf_probe_pipeline SHARED 测试文件模板</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>default-tenant</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>wf_probe_gateway_TPL</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Probe GATEWAY文件模板</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>SHARED</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>WORKFLOW</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>DELIMITED</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>UTF-8</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>UTF-8</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>FALSE</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>\n</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>,</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>"</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>\</t>
+        </is>
+      </c>
+      <c r="N3" t="n">
+        <v>0</v>
+      </c>
+      <c r="O3" t="n">
+        <v>0</v>
+      </c>
+      <c r="P3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q3" t="inlineStr">
+        <is>
+          <t>{}</t>
+        </is>
+      </c>
+      <c r="R3" t="inlineStr">
+        <is>
+          <t>{}</t>
+        </is>
+      </c>
+      <c r="S3" t="inlineStr">
+        <is>
+          <t>NONE</t>
+        </is>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>NONE</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>NONE</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>wf_probe_gateway_${batchDate}.csv</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>[{"source":"id","target":"ID"}]</t>
+        </is>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>{}</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>{}</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AC3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AD3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AE3" t="n">
+        <v>500</v>
+      </c>
+      <c r="AF3" t="inlineStr">
+        <is>
+          <t>FALSE</t>
+        </is>
+      </c>
+      <c r="AG3" t="inlineStr">
+        <is>
+          <t>FALSE</t>
+        </is>
+      </c>
+      <c r="AH3" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AI3" t="inlineStr">
+        <is>
+          <t>FALSE</t>
+        </is>
+      </c>
+      <c r="AK3" t="inlineStr">
+        <is>
+          <t>FALSE</t>
+        </is>
+      </c>
+      <c r="AM3" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AN3" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO3" t="inlineStr">
+        <is>
+          <t>wf_probe_gateway SHARED 测试文件模板</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>default-tenant</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>wf_probe_mixed_TPL</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Probe MIXED文件模板</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>SHARED</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>WORKFLOW</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>DELIMITED</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>UTF-8</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>UTF-8</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>FALSE</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>\n</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>,</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>"</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>\</t>
+        </is>
+      </c>
+      <c r="N4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O4" t="n">
+        <v>0</v>
+      </c>
+      <c r="P4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q4" t="inlineStr">
+        <is>
+          <t>{}</t>
+        </is>
+      </c>
+      <c r="R4" t="inlineStr">
+        <is>
+          <t>{}</t>
+        </is>
+      </c>
+      <c r="S4" t="inlineStr">
+        <is>
+          <t>NONE</t>
+        </is>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>NONE</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>NONE</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>wf_probe_mixed_${batchDate}.csv</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>[{"source":"id","target":"ID"}]</t>
+        </is>
+      </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>{}</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>{}</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AC4" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AD4" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AE4" t="n">
+        <v>500</v>
+      </c>
+      <c r="AF4" t="inlineStr">
+        <is>
+          <t>FALSE</t>
+        </is>
+      </c>
+      <c r="AG4" t="inlineStr">
+        <is>
+          <t>FALSE</t>
+        </is>
+      </c>
+      <c r="AH4" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AI4" t="inlineStr">
+        <is>
+          <t>FALSE</t>
+        </is>
+      </c>
+      <c r="AK4" t="inlineStr">
+        <is>
+          <t>FALSE</t>
+        </is>
+      </c>
+      <c r="AM4" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AN4" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO4" t="inlineStr">
+        <is>
+          <t>wf_probe_mixed SHARED 测试文件模板</t>
         </is>
       </c>
     </row>

--- a/docs/test-data/test-full-coverage-import-suite/default-tenant-config-package-test.xlsx
+++ b/docs/test-data/test-full-coverage-import-suite/default-tenant-config-package-test.xlsx
@@ -1905,7 +1905,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T4"/>
+  <dimension ref="A1:T8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2241,6 +2241,338 @@
       <c r="T4" t="inlineStr">
         <is>
           <t>P2 seed aligned - Probe MIXED</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>default-tenant</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>spi_shell_demo</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>SPI Shell Demo</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>SPI</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>GENERAL</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>spi_queue</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>spi</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>MANUAL</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>always_open</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>EXPONENTIAL</t>
+        </is>
+      </c>
+      <c r="M5" t="n">
+        <v>1</v>
+      </c>
+      <c r="N5" t="n">
+        <v>300</v>
+      </c>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>STATIC</t>
+        </is>
+      </c>
+      <c r="Q5" t="inlineStr">
+        <is>
+          <t>{}</t>
+        </is>
+      </c>
+      <c r="R5" t="inlineStr">
+        <is>
+          <t>{"taskType":"shell","command":"/bin/echo","args":["hello-from-spi"]}</t>
+        </is>
+      </c>
+      <c r="S5" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>SPI demo - SPI Shell Demo</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>default-tenant</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>spi_sql_demo</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>SPI SQL Demo</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>SPI</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>GENERAL</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>spi_queue</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>spi</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>MANUAL</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>always_open</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>EXPONENTIAL</t>
+        </is>
+      </c>
+      <c r="M6" t="n">
+        <v>1</v>
+      </c>
+      <c r="N6" t="n">
+        <v>300</v>
+      </c>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t>STATIC</t>
+        </is>
+      </c>
+      <c r="Q6" t="inlineStr">
+        <is>
+          <t>{}</t>
+        </is>
+      </c>
+      <c r="R6" t="inlineStr">
+        <is>
+          <t>{"taskType":"sql","sql":"SELECT 1"}</t>
+        </is>
+      </c>
+      <c r="S6" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>SPI demo - SPI SQL Demo</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>default-tenant</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>spi_stored_proc_demo</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>SPI Stored Proc Demo</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>SPI</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>GENERAL</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>spi_queue</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>spi</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>MANUAL</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>always_open</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>EXPONENTIAL</t>
+        </is>
+      </c>
+      <c r="M7" t="n">
+        <v>1</v>
+      </c>
+      <c r="N7" t="n">
+        <v>300</v>
+      </c>
+      <c r="O7" t="inlineStr">
+        <is>
+          <t>STATIC</t>
+        </is>
+      </c>
+      <c r="Q7" t="inlineStr">
+        <is>
+          <t>{}</t>
+        </is>
+      </c>
+      <c r="R7" t="inlineStr">
+        <is>
+          <t>{"taskType":"stored_proc","procedureName":"batch.refresh_metrics"}</t>
+        </is>
+      </c>
+      <c r="S7" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>SPI demo - SPI Stored Proc Demo</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>default-tenant</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>spi_http_demo</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>SPI HTTP Demo</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>SPI</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>GENERAL</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>spi_queue</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>spi</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>MANUAL</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>always_open</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>EXPONENTIAL</t>
+        </is>
+      </c>
+      <c r="M8" t="n">
+        <v>1</v>
+      </c>
+      <c r="N8" t="n">
+        <v>300</v>
+      </c>
+      <c r="O8" t="inlineStr">
+        <is>
+          <t>STATIC</t>
+        </is>
+      </c>
+      <c r="Q8" t="inlineStr">
+        <is>
+          <t>{}</t>
+        </is>
+      </c>
+      <c r="R8" t="inlineStr">
+        <is>
+          <t>{"taskType":"http","url":"https://example.internal/health","method":"GET"}</t>
+        </is>
+      </c>
+      <c r="S8" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>SPI demo - SPI HTTP Demo</t>
         </is>
       </c>
     </row>

--- a/docs/test-data/test-full-coverage-import-suite/default-tenant-config-package-test.xlsx
+++ b/docs/test-data/test-full-coverage-import-suite/default-tenant-config-package-test.xlsx
@@ -1905,7 +1905,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T8"/>
+  <dimension ref="A1:U8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2009,6 +2009,11 @@
           <t>description</t>
         </is>
       </c>
+      <c r="U1" t="inlineStr">
+        <is>
+          <t>execution_mode</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -2087,6 +2092,11 @@
           <t>P2 seed aligned - Probe PIPELINE</t>
         </is>
       </c>
+      <c r="U2" t="inlineStr">
+        <is>
+          <t>FULL</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -2165,6 +2175,11 @@
           <t>P2 seed aligned - Probe GATEWAY</t>
         </is>
       </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>FULL</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -2243,6 +2258,11 @@
           <t>P2 seed aligned - Probe MIXED</t>
         </is>
       </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>FULL</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -2326,6 +2346,11 @@
           <t>SPI demo - SPI Shell Demo</t>
         </is>
       </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>FULL</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -2409,6 +2434,11 @@
           <t>SPI demo - SPI SQL Demo</t>
         </is>
       </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>FULL</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -2492,6 +2522,11 @@
           <t>SPI demo - SPI Stored Proc Demo</t>
         </is>
       </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>FULL</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -2573,6 +2608,11 @@
       <c r="T8" t="inlineStr">
         <is>
           <t>SPI demo - SPI HTTP Demo</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>FULL</t>
         </is>
       </c>
     </row>

--- a/docs/test-data/test-full-coverage-import-suite/default-tenant-config-package-test.xlsx
+++ b/docs/test-data/test-full-coverage-import-suite/default-tenant-config-package-test.xlsx
@@ -1905,7 +1905,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U8"/>
+  <dimension ref="A1:W4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1956,62 +1956,72 @@
       </c>
       <c r="J1" t="inlineStr">
         <is>
+          <t>depends_on_job_code</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
           <t>calendar_code</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>window_code</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>retry_policy</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
+      <c r="N1" t="inlineStr">
         <is>
           <t>retry_max_count</t>
         </is>
       </c>
-      <c r="N1" t="inlineStr">
+      <c r="O1" t="inlineStr">
         <is>
           <t>timeout_seconds</t>
         </is>
       </c>
-      <c r="O1" t="inlineStr">
+      <c r="P1" t="inlineStr">
         <is>
           <t>shard_strategy</t>
         </is>
       </c>
-      <c r="P1" t="inlineStr">
+      <c r="Q1" t="inlineStr">
+        <is>
+          <t>execution_mode</t>
+        </is>
+      </c>
+      <c r="R1" t="inlineStr">
+        <is>
+          <t>watermark_field</t>
+        </is>
+      </c>
+      <c r="S1" t="inlineStr">
         <is>
           <t>execution_handler</t>
         </is>
       </c>
-      <c r="Q1" t="inlineStr">
+      <c r="T1" t="inlineStr">
         <is>
           <t>param_schema</t>
         </is>
       </c>
-      <c r="R1" t="inlineStr">
+      <c r="U1" t="inlineStr">
         <is>
           <t>default_params</t>
         </is>
       </c>
-      <c r="S1" t="inlineStr">
+      <c r="V1" t="inlineStr">
         <is>
           <t>enabled</t>
         </is>
       </c>
-      <c r="T1" t="inlineStr">
+      <c r="W1" t="inlineStr">
         <is>
           <t>description</t>
-        </is>
-      </c>
-      <c r="U1" t="inlineStr">
-        <is>
-          <t>execution_mode</t>
         </is>
       </c>
     </row>
@@ -2051,50 +2061,50 @@
           <t>MANUAL</t>
         </is>
       </c>
-      <c r="K2" t="inlineStr">
+      <c r="L2" t="inlineStr">
         <is>
           <t>always_open</t>
         </is>
       </c>
-      <c r="L2" t="inlineStr">
+      <c r="M2" t="inlineStr">
         <is>
           <t>NONE</t>
         </is>
       </c>
-      <c r="M2" t="n">
-        <v>0</v>
-      </c>
       <c r="N2" t="n">
+        <v>0</v>
+      </c>
+      <c r="O2" t="n">
         <v>14400</v>
       </c>
-      <c r="O2" t="inlineStr">
+      <c r="P2" t="inlineStr">
         <is>
           <t>NONE</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
+          <t>FULL</t>
+        </is>
+      </c>
+      <c r="T2" t="inlineStr">
+        <is>
           <t>{}</t>
         </is>
       </c>
-      <c r="R2" t="inlineStr">
+      <c r="U2" t="inlineStr">
         <is>
           <t>{}</t>
         </is>
       </c>
-      <c r="S2" t="inlineStr">
-        <is>
-          <t>TRUE</t>
-        </is>
-      </c>
-      <c r="T2" t="inlineStr">
+      <c r="V2" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="W2" t="inlineStr">
         <is>
           <t>P2 seed aligned - Probe PIPELINE</t>
-        </is>
-      </c>
-      <c r="U2" t="inlineStr">
-        <is>
-          <t>FULL</t>
         </is>
       </c>
     </row>
@@ -2134,50 +2144,50 @@
           <t>MANUAL</t>
         </is>
       </c>
-      <c r="K3" t="inlineStr">
+      <c r="L3" t="inlineStr">
         <is>
           <t>always_open</t>
         </is>
       </c>
-      <c r="L3" t="inlineStr">
+      <c r="M3" t="inlineStr">
         <is>
           <t>NONE</t>
         </is>
       </c>
-      <c r="M3" t="n">
-        <v>0</v>
-      </c>
       <c r="N3" t="n">
+        <v>0</v>
+      </c>
+      <c r="O3" t="n">
         <v>14400</v>
       </c>
-      <c r="O3" t="inlineStr">
+      <c r="P3" t="inlineStr">
         <is>
           <t>NONE</t>
         </is>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
+          <t>FULL</t>
+        </is>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
           <t>{}</t>
         </is>
       </c>
-      <c r="R3" t="inlineStr">
+      <c r="U3" t="inlineStr">
         <is>
           <t>{}</t>
         </is>
       </c>
-      <c r="S3" t="inlineStr">
-        <is>
-          <t>TRUE</t>
-        </is>
-      </c>
-      <c r="T3" t="inlineStr">
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
         <is>
           <t>P2 seed aligned - Probe GATEWAY</t>
-        </is>
-      </c>
-      <c r="U3" t="inlineStr">
-        <is>
-          <t>FULL</t>
         </is>
       </c>
     </row>
@@ -2217,402 +2227,50 @@
           <t>MANUAL</t>
         </is>
       </c>
-      <c r="K4" t="inlineStr">
+      <c r="L4" t="inlineStr">
         <is>
           <t>always_open</t>
         </is>
       </c>
-      <c r="L4" t="inlineStr">
+      <c r="M4" t="inlineStr">
         <is>
           <t>NONE</t>
         </is>
       </c>
-      <c r="M4" t="n">
-        <v>0</v>
-      </c>
       <c r="N4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O4" t="n">
         <v>14400</v>
       </c>
-      <c r="O4" t="inlineStr">
+      <c r="P4" t="inlineStr">
         <is>
           <t>NONE</t>
         </is>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
+          <t>FULL</t>
+        </is>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
           <t>{}</t>
         </is>
       </c>
-      <c r="R4" t="inlineStr">
+      <c r="U4" t="inlineStr">
         <is>
           <t>{}</t>
         </is>
       </c>
-      <c r="S4" t="inlineStr">
-        <is>
-          <t>TRUE</t>
-        </is>
-      </c>
-      <c r="T4" t="inlineStr">
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
         <is>
           <t>P2 seed aligned - Probe MIXED</t>
-        </is>
-      </c>
-      <c r="U4" t="inlineStr">
-        <is>
-          <t>FULL</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>default-tenant</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>spi_shell_demo</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>SPI Shell Demo</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>SPI</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>GENERAL</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>spi_queue</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>spi</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>MANUAL</t>
-        </is>
-      </c>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>always_open</t>
-        </is>
-      </c>
-      <c r="L5" t="inlineStr">
-        <is>
-          <t>EXPONENTIAL</t>
-        </is>
-      </c>
-      <c r="M5" t="n">
-        <v>1</v>
-      </c>
-      <c r="N5" t="n">
-        <v>300</v>
-      </c>
-      <c r="O5" t="inlineStr">
-        <is>
-          <t>STATIC</t>
-        </is>
-      </c>
-      <c r="Q5" t="inlineStr">
-        <is>
-          <t>{}</t>
-        </is>
-      </c>
-      <c r="R5" t="inlineStr">
-        <is>
-          <t>{"taskType":"shell","command":"/bin/echo","args":["hello-from-spi"]}</t>
-        </is>
-      </c>
-      <c r="S5" t="inlineStr">
-        <is>
-          <t>TRUE</t>
-        </is>
-      </c>
-      <c r="T5" t="inlineStr">
-        <is>
-          <t>SPI demo - SPI Shell Demo</t>
-        </is>
-      </c>
-      <c r="U5" t="inlineStr">
-        <is>
-          <t>FULL</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>default-tenant</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>spi_sql_demo</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>SPI SQL Demo</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>SPI</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>GENERAL</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>spi_queue</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>spi</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>MANUAL</t>
-        </is>
-      </c>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>always_open</t>
-        </is>
-      </c>
-      <c r="L6" t="inlineStr">
-        <is>
-          <t>EXPONENTIAL</t>
-        </is>
-      </c>
-      <c r="M6" t="n">
-        <v>1</v>
-      </c>
-      <c r="N6" t="n">
-        <v>300</v>
-      </c>
-      <c r="O6" t="inlineStr">
-        <is>
-          <t>STATIC</t>
-        </is>
-      </c>
-      <c r="Q6" t="inlineStr">
-        <is>
-          <t>{}</t>
-        </is>
-      </c>
-      <c r="R6" t="inlineStr">
-        <is>
-          <t>{"taskType":"sql","sql":"SELECT 1"}</t>
-        </is>
-      </c>
-      <c r="S6" t="inlineStr">
-        <is>
-          <t>TRUE</t>
-        </is>
-      </c>
-      <c r="T6" t="inlineStr">
-        <is>
-          <t>SPI demo - SPI SQL Demo</t>
-        </is>
-      </c>
-      <c r="U6" t="inlineStr">
-        <is>
-          <t>FULL</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>default-tenant</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>spi_stored_proc_demo</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>SPI Stored Proc Demo</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>SPI</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>GENERAL</t>
-        </is>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>spi_queue</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>spi</t>
-        </is>
-      </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>MANUAL</t>
-        </is>
-      </c>
-      <c r="K7" t="inlineStr">
-        <is>
-          <t>always_open</t>
-        </is>
-      </c>
-      <c r="L7" t="inlineStr">
-        <is>
-          <t>EXPONENTIAL</t>
-        </is>
-      </c>
-      <c r="M7" t="n">
-        <v>1</v>
-      </c>
-      <c r="N7" t="n">
-        <v>300</v>
-      </c>
-      <c r="O7" t="inlineStr">
-        <is>
-          <t>STATIC</t>
-        </is>
-      </c>
-      <c r="Q7" t="inlineStr">
-        <is>
-          <t>{}</t>
-        </is>
-      </c>
-      <c r="R7" t="inlineStr">
-        <is>
-          <t>{"taskType":"stored_proc","procedureName":"batch.refresh_metrics"}</t>
-        </is>
-      </c>
-      <c r="S7" t="inlineStr">
-        <is>
-          <t>TRUE</t>
-        </is>
-      </c>
-      <c r="T7" t="inlineStr">
-        <is>
-          <t>SPI demo - SPI Stored Proc Demo</t>
-        </is>
-      </c>
-      <c r="U7" t="inlineStr">
-        <is>
-          <t>FULL</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>default-tenant</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>spi_http_demo</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>SPI HTTP Demo</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>SPI</t>
-        </is>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>GENERAL</t>
-        </is>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>spi_queue</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>spi</t>
-        </is>
-      </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>MANUAL</t>
-        </is>
-      </c>
-      <c r="K8" t="inlineStr">
-        <is>
-          <t>always_open</t>
-        </is>
-      </c>
-      <c r="L8" t="inlineStr">
-        <is>
-          <t>EXPONENTIAL</t>
-        </is>
-      </c>
-      <c r="M8" t="n">
-        <v>1</v>
-      </c>
-      <c r="N8" t="n">
-        <v>300</v>
-      </c>
-      <c r="O8" t="inlineStr">
-        <is>
-          <t>STATIC</t>
-        </is>
-      </c>
-      <c r="Q8" t="inlineStr">
-        <is>
-          <t>{}</t>
-        </is>
-      </c>
-      <c r="R8" t="inlineStr">
-        <is>
-          <t>{"taskType":"http","url":"https://example.internal/health","method":"GET"}</t>
-        </is>
-      </c>
-      <c r="S8" t="inlineStr">
-        <is>
-          <t>TRUE</t>
-        </is>
-      </c>
-      <c r="T8" t="inlineStr">
-        <is>
-          <t>SPI demo - SPI HTTP Demo</t>
-        </is>
-      </c>
-      <c r="U8" t="inlineStr">
-        <is>
-          <t>FULL</t>
         </is>
       </c>
     </row>

--- a/docs/test-data/test-full-coverage-import-suite/default-tenant-config-package-test.xlsx
+++ b/docs/test-data/test-full-coverage-import-suite/default-tenant-config-package-test.xlsx
@@ -1,23 +1,23 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="resource_queue" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="business_calendar" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="batch_window" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="job_definition" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="file_channel_config" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="file_template_config" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet name="pipeline_definition" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet name="pipeline_step_definition" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet name="workflow_definition" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet name="workflow_node" sheetId="10" state="visible" r:id="rId10"/>
-    <sheet name="workflow_edge" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="resource_queue" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="business_calendar" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="batch_window" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="job_definition" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="file_channel_config" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="file_template_config" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="pipeline_definition" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="pipeline_step_definition" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="workflow_definition" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="workflow_node" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="workflow_edge" sheetId="11" state="visible" r:id="rId11"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
